--- a/branches/feat/crmi-artifact-metadata/StructureDefinition-mii-pr-molgen-mikrosatelliteninstabilitaet.xlsx
+++ b/branches/feat/crmi-artifact-metadata/StructureDefinition-mii-pr-molgen-mikrosatelliteninstabilitaet.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:09:33+00:00</t>
+    <t>2026-09-11T10:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
